--- a/_note/convert/Note.xlsx
+++ b/_note/convert/Note.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tantq\src\the-kanji-map\_note\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Tantq\React\the-kanji-map\_note\convert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FCB15C-C9C6-4B20-AD78-18BD12060033}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateCount="1"/>
+  <calcPr calcId="162913" iterateCount="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Update Todos</t>
   </si>
@@ -46,26 +45,197 @@
   </si>
   <si>
     <t>thư mục in tôi đã thay các file .json khác. hãy tiếp tục công việc ở thư mục in từ đầu</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu bạn đang dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claude Code extension trong VS Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và muốn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tự động chọn "Yes"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (không phải bấm Accept mỗi lần), thì có các chế độ sau:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Accept Edits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Tự động chấp nhận các chỉnh sửa file trong project.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mở </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Settings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ctrl + ,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tìm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claude Code: Initial Permission Mode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chọn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>acceptEdits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Khi đó Claude sẽ tự động áp dụng các chỉnh sửa file và một số lệnh an toàn mà không hỏi lại.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -88,8 +258,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,48 +548,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3">
       <c r="C3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3">
       <c r="C5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3">
       <c r="C6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3">
       <c r="C7" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>